--- a/daily/2026-04-04.xlsx
+++ b/daily/2026-04-04.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
         <bgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+        <bgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+        <bgColor rgb="0022C55E"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -66,6 +78,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -793,7 +807,6 @@
       <c r="V4" t="n">
         <v>3</v>
       </c>
-      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
         <v>2.1</v>
       </c>
@@ -1117,7 +1130,6 @@
       <c r="V8" t="n">
         <v>3</v>
       </c>
-      <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
         <v>1.3</v>
       </c>
@@ -1687,7 +1699,6 @@
       <c r="V15" t="n">
         <v>9</v>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="n">
         <v>0</v>
       </c>
@@ -2093,7 +2104,6 @@
       <c r="V20" t="n">
         <v>4</v>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
         <v>4.8</v>
       </c>
@@ -2499,7 +2509,6 @@
       <c r="V25" t="n">
         <v>4</v>
       </c>
-      <c r="W25" t="inlineStr"/>
       <c r="X25" t="n">
         <v>14</v>
       </c>
@@ -5492,303 +5501,693 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Jamal Murray</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>24.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (15 pts vs 24.5 line, -9.5). Underperformed by 9.5 pts — potentially a blowout or garbage-time scenario that pulled starters early. Counter-signals that proved correct: HR L30, HR L10, Defense.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Devin Vassell</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E3" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (18 pts vs 12.5 line, +5.5). Projection model called 17.7 pts — actual 18 was 0.3 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Dylan Harper</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E4" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (12 pts vs 11.5 line, +0.5). Projection model called 13.8 pts — actual 12 was 1.8 off. Model accuracy strong on this play. Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Nikola Jokić</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>26.5</v>
       </c>
+      <c r="E5" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (40 pts vs 26.5 line, +13.5). Overperformed by 13.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Defense, H2H, Pace.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Tim Hardaway Jr.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (10 pts vs 11.5 line, -1.5). Projection model called 8.7 pts — actual 10 was 1.3 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>De'Aaron Fox</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E7" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (14 pts vs 15.5 line, -1.5). Missed by 1.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: HR L30, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Victor Wembanyama</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>28.5</v>
       </c>
+      <c r="E8" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (34 pts vs 28.5 line, +5.5). Projection model targeted 27.4 pts (correct direction) but actual was 34. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Trend, Defense, H2H.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Keldon Johnson</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E9" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (10 pts vs 12.5 line, -2.5). Projection model called 10.4 pts — actual 10 was 0.4 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Christian Braun</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E10" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (21 pts vs 11.5 line, +9.5). Overperformed by 9.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Stephon Castle</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E11" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (20 pts vs 17.5 line, +2.5). Projection model targeted 16.5 pts (correct direction) but actual was 20. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: HR L30, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Julian Champagnie</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E12" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (18 pts vs 9.5 line, +8.5). Signal alignment was sound — 10/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Bruce Brown</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (5 pts vs 6.5 line, -1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: Defense, Min Trend.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Cameron Johnson</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E14" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (17 pts vs 12.5 line, +4.5). Projection model called 15.8 pts — actual 17 was 1.2 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Aaron Gordon</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>SAS @ DEN</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E15" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (15 pts vs 14.5 line, +0.5). Missed by 0.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Kel'el Ware</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>8.5</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (24 pts vs 8.5 line, +15.5). Overperformed by 15.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Volume, HR L30, Context.</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -5810,85 +6209,201 @@
       <c r="D17" t="n">
         <v>13.5</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Davion Mitchell</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E18" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (12 pts vs 10.5 line, +1.5). Missed by 1.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: HR L10, Trend, Defense.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Bilal Coulibaly</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E19" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (12 pts vs 12.5 line, -0.5).</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Will Riley</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E20" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (31 pts vs 15.5 line, +15.5). Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Pelle Larsson</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="4" t="n">
         <v>15.5</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (16 pts vs 15.5 line, +0.5). Projection model called 16.0 pts — actual 16 was 0.0 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -5910,325 +6425,753 @@
       <c r="D22" t="n">
         <v>24.5</v>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E23" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (32 pts vs 16.5 line, +15.5). Overperformed by 15.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: HR L30, Trend, Defense.</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Andrew Wiggins</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E24" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (21 pts vs 15.5 line, +5.5). Projection model targeted 10.7 pts (correct direction) but actual was 21. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Defense, H2H, Pace.</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Tre Johnson</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E25" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (11 pts vs 12.5 line, -1.5). Missed by 1.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Bam Adebayo</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>WAS @ MIA</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>24.5</v>
       </c>
+      <c r="E26" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (14 pts vs 24.5 line, -10.5). Underperformed by 10.5 pts — potentially a blowout or garbage-time scenario that pulled starters early. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Kelly Oubre Jr.</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E27" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (3 pts vs 15.5 line, -12.5). Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Duncan Robinson</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E28" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (11 pts vs 12.5 line, -1.5). Missed by 1.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Daniss Jenkins</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E29" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (16 pts vs 16.5 line, -0.5).</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>VJ Edgecombe</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E30" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (19 pts vs 16.5 line, +2.5). Projection model targeted 12.4 pts (correct direction) but actual was 19. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Kevin Huerter</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E31" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (5 pts vs 9.5 line, -4.5). Projection model (10.4 pts) and actual (5) both missed the mark. Key signals that disagreed: Volume, HR L30, HR L10. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Dominick Barlow</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E32" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (8 pts vs 8.5 line, -0.5). Projection model called 6.3 pts — actual 8 was 1.7 off. Model accuracy strong on this play. Signal alignment was sound — 9/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Tobias Harris</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E33" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (19 pts vs 13.5 line, +5.5). Projection model targeted 11.7 pts (correct direction) but actual was 19. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Trend, Defense, H2H.</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Jalen Duren</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E34" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (16 pts vs 22.5 line, -6.5). Projection model called 18.4 pts — actual 16 was 2.4 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Tyrese Maxey</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>29.5</v>
       </c>
+      <c r="E35" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (23 pts vs 29.5 line, -6.5). Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Quentin Grimes</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (0 pts vs 12.5 line, -12.5).</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Ausar Thompson</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E37" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (14 pts vs 9.5 line, +4.5).</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Adem Bona</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>DET @ PHI</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>5.5</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (10 pts vs 5.5 line, +4.5). Projection model targeted 3.2 pts (correct direction) but actual was 10. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30.</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 07:40</t>
+        </is>
       </c>
     </row>
   </sheetData>
